--- a/escala_medianeira.xlsx
+++ b/escala_medianeira.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfeli\Documents\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D4ED7E9-1EBB-4A11-B2A7-3A4ADA602710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5D0BE3-D1B1-469F-8787-B413261B9AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="99">
   <si>
     <t>Data</t>
   </si>
@@ -104,9 +104,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Marlene</t>
-  </si>
-  <si>
     <t>Elaine</t>
   </si>
   <si>
@@ -131,9 +128,6 @@
     <t>Nalva</t>
   </si>
   <si>
-    <t>Danyella, Fábio</t>
-  </si>
-  <si>
     <t>Bruno</t>
   </si>
   <si>
@@ -149,39 +143,18 @@
     <t>Sirlene</t>
   </si>
   <si>
-    <t>Denise, Antônio</t>
-  </si>
-  <si>
-    <t>Reinaldo</t>
-  </si>
-  <si>
     <t>Marta</t>
   </si>
   <si>
     <t>Claisa</t>
   </si>
   <si>
-    <t>Claudinei</t>
-  </si>
-  <si>
     <t>Renata, Rodolfo</t>
   </si>
   <si>
-    <t>Ane, Juliana Rodrigues</t>
-  </si>
-  <si>
-    <t>Izaías, Marta, Juliana Ricardo, João Ricardo</t>
-  </si>
-  <si>
-    <t>Danyella, Irmã Lica</t>
-  </si>
-  <si>
     <t>Guilherme</t>
   </si>
   <si>
-    <t>Wallace</t>
-  </si>
-  <si>
     <t>Juliana</t>
   </si>
   <si>
@@ -194,147 +167,21 @@
     <t>Terça-Feira</t>
   </si>
   <si>
-    <t>Quarta-Feiira</t>
-  </si>
-  <si>
     <t>Quinta-Feira</t>
   </si>
   <si>
-    <t>Matheus</t>
-  </si>
-  <si>
-    <t>Edivaldo (Didi)</t>
-  </si>
-  <si>
     <t>Alencar</t>
   </si>
   <si>
-    <t>Juliana Rodrigues</t>
-  </si>
-  <si>
     <t>Iolanda</t>
   </si>
   <si>
     <t>Sueli</t>
   </si>
   <si>
-    <t>Marlene, Ester</t>
-  </si>
-  <si>
-    <t>Cristina Sousa, Maria Sousa, Guilherme, Flaviele</t>
-  </si>
-  <si>
-    <t>Ana Cristina, Irmã Lica, Silvio, Sirlene</t>
-  </si>
-  <si>
-    <t>Andreia, Juliana Rodrigues</t>
-  </si>
-  <si>
-    <t>Irmã Neusa, Elaine, Tone, Letícia, Claisa</t>
-  </si>
-  <si>
-    <t>Socorro, Rodolfo, Juliana Ricardo, João Ricardo</t>
-  </si>
-  <si>
-    <t>Mauricio, Ester</t>
-  </si>
-  <si>
     <t>Neiane, Margarida</t>
   </si>
   <si>
-    <t>Renata, Antônio, Denise, Maria Rocha</t>
-  </si>
-  <si>
-    <t>Bruno, Claisa, Andreia</t>
-  </si>
-  <si>
-    <t>Juliana Rodrigues, Rodolfo, Renata, Neiane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wallace, Socorro, Fernanda, Guilherme </t>
-  </si>
-  <si>
-    <t>Irmã Lica, Margarida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andreia, Ane </t>
-  </si>
-  <si>
-    <t>Irmã Neusa, Marisa, Raphael, Ivonete, Maria Rocha</t>
-  </si>
-  <si>
-    <t>Ester, Cristina Sousa, Beto, Mauricio</t>
-  </si>
-  <si>
-    <t>Fernanda, Maria Rocha</t>
-  </si>
-  <si>
-    <t>Margarida, Neiane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elaine, Juliana Rodrigues, Luan, Nalva </t>
-  </si>
-  <si>
-    <t>Izaías, Marta, Guilherme, Luan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cristina Sousa, Fernanda, Maria Sousa, Socorro </t>
-  </si>
-  <si>
-    <t>Iolanda, Nalva, Flaviele, Bruno, Claisa</t>
-  </si>
-  <si>
-    <t>Mauricio, Denise, Antônio, Ane</t>
-  </si>
-  <si>
-    <t>Renata, Ester</t>
-  </si>
-  <si>
-    <t>Denise, Andreia, Antonio, Marlene</t>
-  </si>
-  <si>
-    <t>Sueli, Sirlene, Fátima, Marlene</t>
-  </si>
-  <si>
-    <t>Iolanda, Maria Sousa, Ivonete, Socorro</t>
-  </si>
-  <si>
-    <t>Elaine, Luan, Letícia, Tone, Ane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marlene, Maria Rocha </t>
-  </si>
-  <si>
-    <t>Elaine, Fernanda, Beto, Sirlene</t>
-  </si>
-  <si>
-    <t>Ana Cristina, Guilherme, Irmã Lica, Wallace</t>
-  </si>
-  <si>
-    <t>Letícia, Tone, Raphael, Marisa, Luan</t>
-  </si>
-  <si>
-    <t>Beto, Sueli, Fátima, Maria Vilani</t>
-  </si>
-  <si>
-    <t>Fabio, Danyella</t>
-  </si>
-  <si>
-    <t>Fabio, Danyella, Neiane, Margarida</t>
-  </si>
-  <si>
-    <t>Mauricio</t>
-  </si>
-  <si>
-    <t>Neiane</t>
-  </si>
-  <si>
-    <t>Irmã Lica</t>
-  </si>
-  <si>
-    <t>Rodolfo</t>
-  </si>
-  <si>
     <t>Ester</t>
   </si>
   <si>
@@ -347,7 +194,142 @@
     <t>Marisa</t>
   </si>
   <si>
-    <t>Tone</t>
+    <t>Produção do Tapete de Corpus Christi</t>
+  </si>
+  <si>
+    <t>Quarta-Feira</t>
+  </si>
+  <si>
+    <t>18h</t>
+  </si>
+  <si>
+    <t>Fernanda</t>
+  </si>
+  <si>
+    <t>Fabio| Danyella</t>
+  </si>
+  <si>
+    <t>Cristina</t>
+  </si>
+  <si>
+    <t>Mateus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Paulo </t>
+  </si>
+  <si>
+    <t>Luan</t>
+  </si>
+  <si>
+    <t>Maria Rocha</t>
+  </si>
+  <si>
+    <t>Raphael</t>
+  </si>
+  <si>
+    <t>João</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ester, Rodolfo </t>
+  </si>
+  <si>
+    <t>Raphael, Marisa, Letícia, Tone, Antônio, Denise, Marta, Izaías</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maria Rocha, Marlene </t>
+  </si>
+  <si>
+    <t>Antônio, Denise</t>
+  </si>
+  <si>
+    <t>Bruno, Claisa, Maria Rocha</t>
+  </si>
+  <si>
+    <t>Fernanda, Maurício, Bruno, Claisa</t>
+  </si>
+  <si>
+    <t>Ester, Marlene, Maria Rocha, Socorro</t>
+  </si>
+  <si>
+    <t>Rodolfo, Juliana</t>
+  </si>
+  <si>
+    <t>Cristina Sousa, Letícia, Tone, Guilherme, Ir. Neuza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ane, Beto, Antônio, Denise </t>
+  </si>
+  <si>
+    <t>Fernanda, Marlene</t>
+  </si>
+  <si>
+    <t>Ir. Lica, Margarida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luan, Maria Rocha, Antônio, Denise </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beto, Renata, Ane </t>
+  </si>
+  <si>
+    <t>Maurício, Fábio, Danyella, Sueli</t>
+  </si>
+  <si>
+    <t>Maria Sousa, Wallace, Guilherme, Marlene</t>
+  </si>
+  <si>
+    <t>Raphael, Marisa, Elaine, Letícia, Tone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luan, Maria Rocha, Rodolfo, Renata </t>
+  </si>
+  <si>
+    <t>Ester, Ane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luan, Maria Rocha, Bruno, Maurício </t>
+  </si>
+  <si>
+    <t>Raphael, Marisa, Sueli, Sirlene</t>
+  </si>
+  <si>
+    <t>Maria Sousa, Fernanda, Marlene, Socorro</t>
+  </si>
+  <si>
+    <t>Ane, Andreia</t>
+  </si>
+  <si>
+    <t>Ester, Ir. Neusa, Antônio, Denise, Iolanda</t>
+  </si>
+  <si>
+    <t>Luan, Juliana Ricardo, João Ricardo, Maria Rocha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodolfo, Fernanda </t>
+  </si>
+  <si>
+    <t>Luan, Maria Rocha, Antônio, Denise</t>
+  </si>
+  <si>
+    <t>João Ricardo, Danyella, Bruno, Fábio</t>
+  </si>
+  <si>
+    <t>Ir. Lica, Socorro, Ester, Guilherme</t>
+  </si>
+  <si>
+    <t>Danyella, Fabio</t>
+  </si>
+  <si>
+    <t>Andreia, Juliana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elaine, Cristina Sousa, Denise, Antônio, Claisa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marta, Izaías, Rodolfo, Renata </t>
+  </si>
+  <si>
+    <t>Ester, Maria Rocha</t>
   </si>
 </sst>
 </file>
@@ -395,7 +377,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -446,11 +428,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -478,6 +469,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -781,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.109375" style="8" bestFit="1" customWidth="1"/>
@@ -818,114 +815,98 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
-        <v>46143</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>50</v>
+        <v>46175</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>51</v>
+      <c r="D2" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
-        <v>46143</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>22</v>
-      </c>
+        <v>46176</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
-        <v>46143</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>22</v>
-      </c>
+        <v>46176</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
-        <v>46144</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>28</v>
+        <v>46177</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46144</v>
+        <v>46178</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>22</v>
@@ -933,45 +914,45 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
-        <v>46145</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>29</v>
+        <v>46178</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>98</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>46145</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>29</v>
+        <v>46178</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>22</v>
@@ -979,68 +960,68 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>46145</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>29</v>
+        <v>46179</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>46145</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>29</v>
+        <v>46179</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>46145</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>29</v>
+        <v>46179</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>22</v>
@@ -1048,45 +1029,45 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
-        <v>46145</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>29</v>
+        <v>46180</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
-        <v>46147</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>52</v>
+        <v>46180</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>22</v>
@@ -1094,114 +1075,115 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
-        <v>46148</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>53</v>
+        <v>46180</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
-        <v>46148</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>53</v>
+        <v>46180</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>22</v>
+        <v>73</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
-        <v>46149</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>54</v>
+        <v>46180</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>46150</v>
+        <v>46180</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
-        <v>46150</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>50</v>
+        <f>A17+2</f>
+        <v>46182</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>22</v>
@@ -1209,22 +1191,22 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
-        <v>46151</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>46183</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>22</v>
@@ -1232,91 +1214,91 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
-        <v>46151</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>46183</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
-        <v>46151</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>28</v>
+        <v>46184</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
-        <v>46152</v>
+        <v>46185</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
-        <v>46152</v>
+        <v>46186</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>22</v>
@@ -1324,22 +1306,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
-        <v>46152</v>
+        <v>46186</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>22</v>
@@ -1347,45 +1329,45 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
-        <v>46152</v>
+        <v>46187</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
-        <v>46152</v>
+        <v>46187</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>22</v>
@@ -1393,68 +1375,68 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
-        <v>46152</v>
+        <v>46187</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
-        <v>46154</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>46187</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
-        <v>46155</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>53</v>
+        <v>46187</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>22</v>
@@ -1462,33 +1444,34 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
-        <v>46155</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>53</v>
+        <v>46187</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
-        <v>46156</v>
+        <f>A30+2</f>
+        <v>46189</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>12</v>
@@ -1497,33 +1480,33 @@
         <v>5</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
-        <v>46157</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>50</v>
+        <v>46190</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>22</v>
@@ -1531,22 +1514,22 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
-        <v>46157</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>50</v>
+        <v>46190</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>22</v>
@@ -1554,45 +1537,45 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
-        <v>46158</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>28</v>
+        <v>46191</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
-        <v>46158</v>
+        <v>46192</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>22</v>
@@ -1600,45 +1583,45 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
-        <v>46159</v>
+        <v>46192</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
-        <v>46159</v>
+        <v>46193</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>22</v>
@@ -1646,68 +1629,68 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
-        <v>46159</v>
+        <v>46193</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
-        <v>46159</v>
+        <v>46194</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
-        <v>46159</v>
+        <v>46194</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>22</v>
@@ -1715,68 +1698,68 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
-        <v>46159</v>
+        <v>46194</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
-        <v>46161</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>52</v>
+        <v>46194</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
-        <v>46162</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>53</v>
+        <v>46194</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>22</v>
@@ -1784,33 +1767,34 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
-        <v>46162</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>53</v>
+        <v>46194</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
-        <v>46163</v>
+        <f>A44+2</f>
+        <v>46196</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>12</v>
@@ -1819,33 +1803,33 @@
         <v>5</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
-        <v>46164</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>50</v>
+        <v>46197</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>22</v>
@@ -1853,22 +1837,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
-        <v>46164</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>50</v>
+        <v>46197</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>5</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>22</v>
@@ -1876,42 +1860,42 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
-        <v>46165</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>28</v>
+        <v>46198</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
-        <v>46165</v>
+        <v>46199</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>34</v>
@@ -1922,45 +1906,45 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
-        <v>46166</v>
+        <v>46199</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
-        <v>46166</v>
+        <v>46200</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>21</v>
+        <v>7</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>22</v>
@@ -1968,68 +1952,68 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
-        <v>46166</v>
+        <v>46200</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
-        <v>46166</v>
+        <v>46201</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
-        <v>46166</v>
+        <v>46201</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>22</v>
@@ -2037,68 +2021,68 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
-        <v>46166</v>
+        <v>46201</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
-        <v>46168</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>52</v>
+        <v>46201</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
-        <v>46169</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>53</v>
+        <v>46201</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>22</v>
@@ -2106,33 +2090,34 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
-        <v>46169</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>53</v>
+        <v>46201</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
-        <v>46170</v>
+        <f>A58+2</f>
+        <v>46203</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>12</v>
@@ -2141,246 +2126,62 @@
         <v>5</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>102</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G59" s="4"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="8">
-        <v>46171</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="B60" s="3"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="3"/>
+      <c r="G60" s="4"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="8">
-        <v>46171</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="B61" s="3"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="3"/>
+      <c r="G61" s="4"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="8">
-        <v>46172</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>97</v>
-      </c>
+      <c r="B62" s="3"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="3"/>
+      <c r="G62" s="4"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="8">
-        <v>46172</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="6"/>
+      <c r="G63" s="4"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="8">
-        <v>46173</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="8">
-        <v>46173</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="8">
-        <v>46173</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="8">
-        <v>46173</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="8">
-        <v>46173</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="8">
-        <v>46173</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="3"/>
+      <c r="G64" s="4"/>
+    </row>
+    <row r="65" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C65" s="2"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="3"/>
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C66" s="2"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="3"/>
+      <c r="G66" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/escala_medianeira.xlsx
+++ b/escala_medianeira.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfeli\Documents\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5D0BE3-D1B1-469F-8787-B413261B9AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B128BB69-AED7-4ED1-B451-C325FB732761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2096,7 +2096,7 @@
         <v>28</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>55</v>

--- a/escala_medianeira.xlsx
+++ b/escala_medianeira.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfeli\Documents\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B128BB69-AED7-4ED1-B451-C325FB732761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8FF33A-4C52-4C09-BE04-60B1E2E7F917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="98">
   <si>
     <t>Data</t>
   </si>
@@ -227,9 +227,6 @@
     <t>Raphael</t>
   </si>
   <si>
-    <t>João</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ester, Rodolfo </t>
   </si>
   <si>
@@ -311,9 +308,6 @@
     <t>Luan, Maria Rocha, Antônio, Denise</t>
   </si>
   <si>
-    <t>João Ricardo, Danyella, Bruno, Fábio</t>
-  </si>
-  <si>
     <t>Ir. Lica, Socorro, Ester, Guilherme</t>
   </si>
   <si>
@@ -330,6 +324,9 @@
   </si>
   <si>
     <t>Ester, Maria Rocha</t>
+  </si>
+  <si>
+    <t>Juliana Ricardo, Danyella, Bruno, Fábio</t>
   </si>
 </sst>
 </file>
@@ -830,7 +827,7 @@
         <v>19</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>22</v>
@@ -883,7 +880,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>52</v>
@@ -906,7 +903,7 @@
         <v>6</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>22</v>
@@ -952,7 +949,7 @@
         <v>6</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>22</v>
@@ -975,7 +972,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>37</v>
@@ -998,7 +995,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>56</v>
@@ -1044,7 +1041,7 @@
         <v>19</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>49</v>
@@ -1090,7 +1087,7 @@
         <v>19</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>22</v>
@@ -1113,7 +1110,7 @@
         <v>6</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>58</v>
@@ -1159,7 +1156,7 @@
         <v>6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>51</v>
@@ -1183,7 +1180,7 @@
         <v>6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>22</v>
@@ -1206,7 +1203,7 @@
         <v>6</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>22</v>
@@ -1252,7 +1249,7 @@
         <v>6</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>25</v>
@@ -1275,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>22</v>
@@ -1298,7 +1295,7 @@
         <v>6</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>22</v>
@@ -1344,7 +1341,7 @@
         <v>19</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>39</v>
@@ -1367,7 +1364,7 @@
         <v>21</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>22</v>
@@ -1390,7 +1387,7 @@
         <v>6</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>22</v>
@@ -1413,7 +1410,7 @@
         <v>6</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>23</v>
@@ -1459,7 +1456,7 @@
         <v>6</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>61</v>
@@ -1483,7 +1480,7 @@
         <v>19</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>22</v>
@@ -1506,7 +1503,7 @@
         <v>19</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>22</v>
@@ -1552,7 +1549,7 @@
         <v>6</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>62</v>
@@ -1598,7 +1595,7 @@
         <v>19</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>22</v>
@@ -1644,7 +1641,7 @@
         <v>6</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>63</v>
@@ -1667,7 +1664,7 @@
         <v>19</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>24</v>
@@ -1713,7 +1710,7 @@
         <v>20</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>22</v>
@@ -1736,7 +1733,7 @@
         <v>6</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>49</v>
@@ -1782,7 +1779,7 @@
         <v>6</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>40</v>
@@ -1806,7 +1803,7 @@
         <v>19</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>22</v>
@@ -1829,7 +1826,7 @@
         <v>6</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>22</v>
@@ -1875,7 +1872,7 @@
         <v>6</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>50</v>
@@ -1967,10 +1964,10 @@
         <v>6</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -1990,7 +1987,7 @@
         <v>19</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>39</v>
@@ -2013,7 +2010,7 @@
         <v>18</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>22</v>
@@ -2036,7 +2033,7 @@
         <v>6</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>22</v>
@@ -2059,7 +2056,7 @@
         <v>6</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>58</v>
@@ -2105,7 +2102,7 @@
         <v>6</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>36</v>
@@ -2129,7 +2126,7 @@
         <v>19</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G59" s="4"/>
     </row>
